--- a/Structure_Data/text.9.14/20260914_88/structure_factor_20260914_88.xlsx
+++ b/Structure_Data/text.9.14/20260914_88/structure_factor_20260914_88.xlsx
@@ -40,7 +40,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:D344"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -248,6 +248,3536 @@
         <v>35.7368013176217</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度 beta / Constrictivity (x)</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈半径 r_min (um)</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">孔体半径 r_max (um)</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度状态 / Constrictivity Status</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">侵入入口 / Intrusion Inlet</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球心邻域 / Center Connectivity</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">算法版本 / Method</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">edt_critical_radii_closed_dilation_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半径采样 / Radius Sampling</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All positive EDT values</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius (um)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPSD (total volume fraction)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIP (total volume fraction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30">
+        <v>0.225189208984375</v>
+      </c>
+      <c r="C30">
+        <v>0.223232269287109</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.5</v>
+      </c>
+      <c r="B31">
+        <v>0.225189208984375</v>
+      </c>
+      <c r="C31">
+        <v>0.223232269287109</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B32">
+        <v>0.100971221923828</v>
+      </c>
+      <c r="C32">
+        <v>0.00327682495117188</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B33">
+        <v>0.0229606628417969</v>
+      </c>
+      <c r="C33">
+        <v>0.000244140625</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34">
+        <v>0.0127067565917969</v>
+      </c>
+      <c r="C34">
+        <v>0.00016021728515625</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B35">
+        <v>0.00696563720703125</v>
+      </c>
+      <c r="C35">
+        <v>0.000125885009765625</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B36">
+        <v>0.0011138916015625</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B37">
+        <v>0.0004730224609375</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>1.5</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">弦长分布 / Chord Length</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_voxel_runs_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>23410</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>1.26082870568133</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>1.00648007061982</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Axis</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Window-spanning lines</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full pore line policy</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one_period_censored</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.05</v>
+      </c>
+      <c r="B54">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.1</v>
+      </c>
+      <c r="B55">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.15</v>
+      </c>
+      <c r="B56">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.2</v>
+      </c>
+      <c r="B57">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.25</v>
+      </c>
+      <c r="B58">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.3</v>
+      </c>
+      <c r="B59">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.35</v>
+      </c>
+      <c r="B60">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.4</v>
+      </c>
+      <c r="B61">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.45</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.5</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.55</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.6</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.65</v>
+      </c>
+      <c r="B66">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.7</v>
+      </c>
+      <c r="B67">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.75</v>
+      </c>
+      <c r="B68">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.8</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.85</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.9</v>
+      </c>
+      <c r="B71">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.95</v>
+      </c>
+      <c r="B72">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.5</v>
+      </c>
+      <c r="B74">
+        <v>9486</v>
+      </c>
+      <c r="C74">
+        <v>0.405211448099103</v>
+      </c>
+      <c r="D74">
+        <v>0.405211448099103</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>1</v>
+      </c>
+      <c r="B75">
+        <v>5602</v>
+      </c>
+      <c r="C75">
+        <v>0.23929944468176</v>
+      </c>
+      <c r="D75">
+        <v>0.644510892780863</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>1.5</v>
+      </c>
+      <c r="B76">
+        <v>3199</v>
+      </c>
+      <c r="C76">
+        <v>0.136651003844511</v>
+      </c>
+      <c r="D76">
+        <v>0.781161896625374</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>2</v>
+      </c>
+      <c r="B77">
+        <v>1976</v>
+      </c>
+      <c r="C77">
+        <v>0.0844083724903887</v>
+      </c>
+      <c r="D77">
+        <v>0.865570269115763</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>2.5</v>
+      </c>
+      <c r="B78">
+        <v>1215</v>
+      </c>
+      <c r="C78">
+        <v>0.0519008970525416</v>
+      </c>
+      <c r="D78">
+        <v>0.917471166168304</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>3</v>
+      </c>
+      <c r="B79">
+        <v>716</v>
+      </c>
+      <c r="C79">
+        <v>0.0305852199914566</v>
+      </c>
+      <c r="D79">
+        <v>0.948056386159761</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>3.5</v>
+      </c>
+      <c r="B80">
+        <v>467</v>
+      </c>
+      <c r="C80">
+        <v>0.0199487398547629</v>
+      </c>
+      <c r="D80">
+        <v>0.968005126014524</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>4</v>
+      </c>
+      <c r="B81">
+        <v>287</v>
+      </c>
+      <c r="C81">
+        <v>0.0122597180692012</v>
+      </c>
+      <c r="D81">
+        <v>0.980264844083725</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>4.5</v>
+      </c>
+      <c r="B82">
+        <v>176</v>
+      </c>
+      <c r="C82">
+        <v>0.00751815463477147</v>
+      </c>
+      <c r="D82">
+        <v>0.987782998718496</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>5</v>
+      </c>
+      <c r="B83">
+        <v>116</v>
+      </c>
+      <c r="C83">
+        <v>0.00495514737291756</v>
+      </c>
+      <c r="D83">
+        <v>0.992738146091414</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>5.5</v>
+      </c>
+      <c r="B84">
+        <v>61</v>
+      </c>
+      <c r="C84">
+        <v>0.00260572404955147</v>
+      </c>
+      <c r="D84">
+        <v>0.995343870140965</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>6</v>
+      </c>
+      <c r="B85">
+        <v>38</v>
+      </c>
+      <c r="C85">
+        <v>0.00162323793250748</v>
+      </c>
+      <c r="D85">
+        <v>0.996967108073473</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>6.5</v>
+      </c>
+      <c r="B86">
+        <v>28</v>
+      </c>
+      <c r="C86">
+        <v>0.00119607005553182</v>
+      </c>
+      <c r="D86">
+        <v>0.998163178129005</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>7</v>
+      </c>
+      <c r="B87">
+        <v>16</v>
+      </c>
+      <c r="C87">
+        <v>0.000683468603161042</v>
+      </c>
+      <c r="D87">
+        <v>0.998846646732166</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>7.5</v>
+      </c>
+      <c r="B88">
+        <v>11</v>
+      </c>
+      <c r="C88">
+        <v>0.000469884664673217</v>
+      </c>
+      <c r="D88">
+        <v>0.999316531396839</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>8</v>
+      </c>
+      <c r="B89">
+        <v>4</v>
+      </c>
+      <c r="C89">
+        <v>0.000170867150790261</v>
+      </c>
+      <c r="D89">
+        <v>0.999487398547629</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>8.5</v>
+      </c>
+      <c r="B90">
+        <v>4</v>
+      </c>
+      <c r="C90">
+        <v>0.000170867150790261</v>
+      </c>
+      <c r="D90">
+        <v>0.999658265698419</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>9</v>
+      </c>
+      <c r="B91">
+        <v>5</v>
+      </c>
+      <c r="C91">
+        <v>0.000213583938487826</v>
+      </c>
+      <c r="D91">
+        <v>0.999871849636907</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>9.5</v>
+      </c>
+      <c r="B92">
+        <v>1</v>
+      </c>
+      <c r="C92">
+        <v>4.27167876975651e-05</v>
+      </c>
+      <c r="D92">
+        <v>0.999914566424605</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>10</v>
+      </c>
+      <c r="B93">
+        <v>2</v>
+      </c>
+      <c r="C93">
+        <v>8.54335753951303e-05</v>
+      </c>
+      <c r="D93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94"/>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球接触分布 / Spherical Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_solid_to_pore_edt_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B99">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B101">
+        <v>203112</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>0.764129968331045</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>0.373613130430095</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance direction</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">solid_to_pore</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance convention</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voxel_center_to_voxel_center</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>0.05</v>
+      </c>
+      <c r="B108">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>0.1</v>
+      </c>
+      <c r="B109">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>0.15</v>
+      </c>
+      <c r="B110">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>0.2</v>
+      </c>
+      <c r="B111">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>0.25</v>
+      </c>
+      <c r="B112">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>0.3</v>
+      </c>
+      <c r="B113">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>0.35</v>
+      </c>
+      <c r="B114">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>0.4</v>
+      </c>
+      <c r="B115">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>0.45</v>
+      </c>
+      <c r="B116">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>0.5</v>
+      </c>
+      <c r="B117">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>0.55</v>
+      </c>
+      <c r="B118">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>0.6</v>
+      </c>
+      <c r="B119">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>0.65</v>
+      </c>
+      <c r="B120">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>0.7</v>
+      </c>
+      <c r="B121">
+        <v>0.866025403784439</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>0.75</v>
+      </c>
+      <c r="B122">
+        <v>0.866025403784439</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>0.8</v>
+      </c>
+      <c r="B123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>0.85</v>
+      </c>
+      <c r="B124">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>0.9</v>
+      </c>
+      <c r="B125">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>0.95</v>
+      </c>
+      <c r="B126">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>0.5</v>
+      </c>
+      <c r="B128">
+        <v>90667</v>
+      </c>
+      <c r="C128">
+        <v>0.44638918429241</v>
+      </c>
+      <c r="D128">
+        <v>0.44638918429241</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B129">
+        <v>50996</v>
+      </c>
+      <c r="C129">
+        <v>0.251073299460396</v>
+      </c>
+      <c r="D129">
+        <v>0.697462483752806</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B130">
+        <v>16548</v>
+      </c>
+      <c r="C130">
+        <v>0.0814722911497105</v>
+      </c>
+      <c r="D130">
+        <v>0.778934774902517</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>1</v>
+      </c>
+      <c r="B131">
+        <v>10656</v>
+      </c>
+      <c r="C131">
+        <v>0.0524636653668912</v>
+      </c>
+      <c r="D131">
+        <v>0.831398440269408</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B132">
+        <v>15039</v>
+      </c>
+      <c r="C132">
+        <v>0.0740428925912797</v>
+      </c>
+      <c r="D132">
+        <v>0.905441332860688</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B133">
+        <v>4889</v>
+      </c>
+      <c r="C133">
+        <v>0.0240704635865926</v>
+      </c>
+      <c r="D133">
+        <v>0.92951179644728</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B134">
+        <v>1812</v>
+      </c>
+      <c r="C134">
+        <v>0.00892118634054118</v>
+      </c>
+      <c r="D134">
+        <v>0.938432982787822</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>1.5</v>
+      </c>
+      <c r="B135">
+        <v>2928</v>
+      </c>
+      <c r="C135">
+        <v>0.0144156918350467</v>
+      </c>
+      <c r="D135">
+        <v>0.952848674622868</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B136">
+        <v>1564</v>
+      </c>
+      <c r="C136">
+        <v>0.00770018511953996</v>
+      </c>
+      <c r="D136">
+        <v>0.960548859742408</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B137">
+        <v>1171</v>
+      </c>
+      <c r="C137">
+        <v>0.00576529205561464</v>
+      </c>
+      <c r="D137">
+        <v>0.966314151798023</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B138">
+        <v>393</v>
+      </c>
+      <c r="C138">
+        <v>0.00193489306392532</v>
+      </c>
+      <c r="D138">
+        <v>0.968249044861948</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B139">
+        <v>949</v>
+      </c>
+      <c r="C139">
+        <v>0.00467229902713774</v>
+      </c>
+      <c r="D139">
+        <v>0.972921343889086</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>1.87082869338697</v>
+      </c>
+      <c r="B140">
+        <v>1325</v>
+      </c>
+      <c r="C140">
+        <v>0.00652349442672023</v>
+      </c>
+      <c r="D140">
+        <v>0.979444838315806</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>2</v>
+      </c>
+      <c r="B141">
+        <v>161</v>
+      </c>
+      <c r="C141">
+        <v>0.00079266611524676</v>
+      </c>
+      <c r="D141">
+        <v>0.980237504431053</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>2.06155281280883</v>
+      </c>
+      <c r="B142">
+        <v>989</v>
+      </c>
+      <c r="C142">
+        <v>0.00486923470794439</v>
+      </c>
+      <c r="D142">
+        <v>0.985106739138997</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>2.12132034355964</v>
+      </c>
+      <c r="B143">
+        <v>491</v>
+      </c>
+      <c r="C143">
+        <v>0.00241738548190161</v>
+      </c>
+      <c r="D143">
+        <v>0.987524124620899</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>2.17944947177034</v>
+      </c>
+      <c r="B144">
+        <v>278</v>
+      </c>
+      <c r="C144">
+        <v>0.00136870298160621</v>
+      </c>
+      <c r="D144">
+        <v>0.988892827602505</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>2.23606797749979</v>
+      </c>
+      <c r="B145">
+        <v>246</v>
+      </c>
+      <c r="C145">
+        <v>0.00121115443696089</v>
+      </c>
+      <c r="D145">
+        <v>0.990103982039466</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>2.29128784747792</v>
+      </c>
+      <c r="B146">
+        <v>392</v>
+      </c>
+      <c r="C146">
+        <v>0.00192996967190516</v>
+      </c>
+      <c r="D146">
+        <v>0.992033951711371</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>2.34520787991171</v>
+      </c>
+      <c r="B147">
+        <v>177</v>
+      </c>
+      <c r="C147">
+        <v>0.00087144038756942</v>
+      </c>
+      <c r="D147">
+        <v>0.99290539209894</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>2.44948974278318</v>
+      </c>
+      <c r="B148">
+        <v>158</v>
+      </c>
+      <c r="C148">
+        <v>0.000777895939186262</v>
+      </c>
+      <c r="D148">
+        <v>0.993683288038127</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>2.5</v>
+      </c>
+      <c r="B149">
+        <v>164</v>
+      </c>
+      <c r="C149">
+        <v>0.000807436291307259</v>
+      </c>
+      <c r="D149">
+        <v>0.994490724329434</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>2.54950975679639</v>
+      </c>
+      <c r="B150">
+        <v>310</v>
+      </c>
+      <c r="C150">
+        <v>0.00152625152625153</v>
+      </c>
+      <c r="D150">
+        <v>0.996016975855685</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>2.59807621135332</v>
+      </c>
+      <c r="B151">
+        <v>97</v>
+      </c>
+      <c r="C151">
+        <v>0.000477569025956123</v>
+      </c>
+      <c r="D151">
+        <v>0.996494544881642</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>2.69258240356725</v>
+      </c>
+      <c r="B152">
+        <v>207</v>
+      </c>
+      <c r="C152">
+        <v>0.00101914214817441</v>
+      </c>
+      <c r="D152">
+        <v>0.997513687029816</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>2.73861278752583</v>
+      </c>
+      <c r="B153">
+        <v>72</v>
+      </c>
+      <c r="C153">
+        <v>0.000354484225451967</v>
+      </c>
+      <c r="D153">
+        <v>0.997868171255268</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>2.82842712474619</v>
+      </c>
+      <c r="B154">
+        <v>26</v>
+      </c>
+      <c r="C154">
+        <v>0.000128008192524322</v>
+      </c>
+      <c r="D154">
+        <v>0.997996179447792</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>2.87228132326901</v>
+      </c>
+      <c r="B155">
+        <v>84</v>
+      </c>
+      <c r="C155">
+        <v>0.000413564929693962</v>
+      </c>
+      <c r="D155">
+        <v>0.998409744377486</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>2.91547594742265</v>
+      </c>
+      <c r="B156">
+        <v>65</v>
+      </c>
+      <c r="C156">
+        <v>0.000320020481310804</v>
+      </c>
+      <c r="D156">
+        <v>0.998729764858797</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>2.95803989154981</v>
+      </c>
+      <c r="B157">
+        <v>47</v>
+      </c>
+      <c r="C157">
+        <v>0.000231399424947812</v>
+      </c>
+      <c r="D157">
+        <v>0.998961164283745</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>3</v>
+      </c>
+      <c r="B158">
+        <v>29</v>
+      </c>
+      <c r="C158">
+        <v>0.00014277836858482</v>
+      </c>
+      <c r="D158">
+        <v>0.99910394265233</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>3.04138126514911</v>
+      </c>
+      <c r="B159">
+        <v>10</v>
+      </c>
+      <c r="C159">
+        <v>4.92339202016621e-05</v>
+      </c>
+      <c r="D159">
+        <v>0.999153176572531</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>3.08220700148449</v>
+      </c>
+      <c r="B160">
+        <v>54</v>
+      </c>
+      <c r="C160">
+        <v>0.000265863169088976</v>
+      </c>
+      <c r="D160">
+        <v>0.99941903974162</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>3.16227766016838</v>
+      </c>
+      <c r="B161">
+        <v>5</v>
+      </c>
+      <c r="C161">
+        <v>2.46169601008311e-05</v>
+      </c>
+      <c r="D161">
+        <v>0.999443656701721</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>3.20156211871642</v>
+      </c>
+      <c r="B162">
+        <v>43</v>
+      </c>
+      <c r="C162">
+        <v>0.000211705856867147</v>
+      </c>
+      <c r="D162">
+        <v>0.999655362558588</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>3.24037034920393</v>
+      </c>
+      <c r="B163">
+        <v>13</v>
+      </c>
+      <c r="C163">
+        <v>6.40040962621608e-05</v>
+      </c>
+      <c r="D163">
+        <v>0.999719366654851</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>3.278719262151</v>
+      </c>
+      <c r="B164">
+        <v>14</v>
+      </c>
+      <c r="C164">
+        <v>6.8927488282327e-05</v>
+      </c>
+      <c r="D164">
+        <v>0.999788294143133</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>3.3166247903554</v>
+      </c>
+      <c r="B165">
+        <v>6</v>
+      </c>
+      <c r="C165">
+        <v>2.95403521209973e-05</v>
+      </c>
+      <c r="D165">
+        <v>0.999817834495254</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>3.35410196624968</v>
+      </c>
+      <c r="B166">
+        <v>12</v>
+      </c>
+      <c r="C166">
+        <v>5.90807042419946e-05</v>
+      </c>
+      <c r="D166">
+        <v>0.999876915199496</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>3.39116499156263</v>
+      </c>
+      <c r="B167">
+        <v>8</v>
+      </c>
+      <c r="C167">
+        <v>3.93871361613297e-05</v>
+      </c>
+      <c r="D167">
+        <v>0.999916302335657</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>3.46410161513775</v>
+      </c>
+      <c r="B168">
+        <v>1</v>
+      </c>
+      <c r="C168">
+        <v>4.92339202016621e-06</v>
+      </c>
+      <c r="D168">
+        <v>0.999921225727677</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>3.5</v>
+      </c>
+      <c r="B169">
+        <v>4</v>
+      </c>
+      <c r="C169">
+        <v>1.96935680806649e-05</v>
+      </c>
+      <c r="D169">
+        <v>0.999940919295758</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>3.53553390593274</v>
+      </c>
+      <c r="B170">
+        <v>4</v>
+      </c>
+      <c r="C170">
+        <v>1.96935680806649e-05</v>
+      </c>
+      <c r="D170">
+        <v>0.999960612863839</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>3.57071421427143</v>
+      </c>
+      <c r="B171">
+        <v>3</v>
+      </c>
+      <c r="C171">
+        <v>1.47701760604986e-05</v>
+      </c>
+      <c r="D171">
+        <v>0.999975383039899</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>3.64005494464026</v>
+      </c>
+      <c r="B172">
+        <v>3</v>
+      </c>
+      <c r="C172">
+        <v>1.47701760604986e-05</v>
+      </c>
+      <c r="D172">
+        <v>0.99999015321596</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>3.67423461417477</v>
+      </c>
+      <c r="B173">
+        <v>1</v>
+      </c>
+      <c r="C173">
+        <v>4.92339202016621e-06</v>
+      </c>
+      <c r="D173">
+        <v>0.99999507660798</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>3.74165738677394</v>
+      </c>
+      <c r="B174">
+        <v>1</v>
+      </c>
+      <c r="C174">
+        <v>4.92339202016621e-06</v>
+      </c>
+      <c r="D174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175"/>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">两点相关函数 / Two-Point Correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_fft_radial_shells_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Porosity</t>
+        </is>
+      </c>
+      <c r="B180">
+        <v>0.225189208984375</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B181">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radial bins</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bin_0_origin_only; bin_k: (k-1)*h &lt; distance &lt;= k*h</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normalization</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">joint_probability; C(0)=porosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius upper edge (um)</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displacement count</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean distance (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <v>0</v>
+      </c>
+      <c r="B186">
+        <v>0.225189208984375</v>
+      </c>
+      <c r="C186">
+        <v>1</v>
+      </c>
+      <c r="D186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <v>0.5</v>
+      </c>
+      <c r="B187">
+        <v>0.126885732014974</v>
+      </c>
+      <c r="C187">
+        <v>6</v>
+      </c>
+      <c r="D187">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <v>1</v>
+      </c>
+      <c r="B188">
+        <v>0.093995607816256</v>
+      </c>
+      <c r="C188">
+        <v>26</v>
+      </c>
+      <c r="D188">
+        <v>0.82359556171208</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>1.5</v>
+      </c>
+      <c r="B189">
+        <v>0.0681576199001736</v>
+      </c>
+      <c r="C189">
+        <v>90</v>
+      </c>
+      <c r="D189">
+        <v>1.31330283768748</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>2</v>
+      </c>
+      <c r="B190">
+        <v>0.0592212961680854</v>
+      </c>
+      <c r="C190">
+        <v>134</v>
+      </c>
+      <c r="D190">
+        <v>1.76619125712671</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>2.5</v>
+      </c>
+      <c r="B191">
+        <v>0.0576399869697038</v>
+      </c>
+      <c r="C191">
+        <v>258</v>
+      </c>
+      <c r="D191">
+        <v>2.25329087515144</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>3</v>
+      </c>
+      <c r="B192">
+        <v>0.057577216915968</v>
+      </c>
+      <c r="C192">
+        <v>410</v>
+      </c>
+      <c r="D192">
+        <v>2.77015092047628</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>3.5</v>
+      </c>
+      <c r="B193">
+        <v>0.0574260974219936</v>
+      </c>
+      <c r="C193">
+        <v>494</v>
+      </c>
+      <c r="D193">
+        <v>3.26511495914839</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>4</v>
+      </c>
+      <c r="B194">
+        <v>0.0569406924040421</v>
+      </c>
+      <c r="C194">
+        <v>690</v>
+      </c>
+      <c r="D194">
+        <v>3.74137726298534</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <v>4.5</v>
+      </c>
+      <c r="B195">
+        <v>0.0564063343833241</v>
+      </c>
+      <c r="C195">
+        <v>962</v>
+      </c>
+      <c r="D195">
+        <v>4.25479734207796</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <v>5</v>
+      </c>
+      <c r="B196">
+        <v>0.0559931617834095</v>
+      </c>
+      <c r="C196">
+        <v>1098</v>
+      </c>
+      <c r="D196">
+        <v>4.75998893674797</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197">
+        <v>5.5</v>
+      </c>
+      <c r="B197">
+        <v>0.0555273519979941</v>
+      </c>
+      <c r="C197">
+        <v>1406</v>
+      </c>
+      <c r="D197">
+        <v>5.25297061080461</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198">
+        <v>6</v>
+      </c>
+      <c r="B198">
+        <v>0.0550395786686693</v>
+      </c>
+      <c r="C198">
+        <v>1578</v>
+      </c>
+      <c r="D198">
+        <v>5.7433060626392</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199">
+        <v>6.5</v>
+      </c>
+      <c r="B199">
+        <v>0.0546812618924794</v>
+      </c>
+      <c r="C199">
+        <v>2018</v>
+      </c>
+      <c r="D199">
+        <v>6.24308779578354</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200">
+        <v>7</v>
+      </c>
+      <c r="B200">
+        <v>0.054305538369691</v>
+      </c>
+      <c r="C200">
+        <v>2342</v>
+      </c>
+      <c r="D200">
+        <v>6.75452277955052</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201">
+        <v>7.5</v>
+      </c>
+      <c r="B201">
+        <v>0.0539505045433884</v>
+      </c>
+      <c r="C201">
+        <v>2634</v>
+      </c>
+      <c r="D201">
+        <v>7.25880828593797</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202">
+        <v>8</v>
+      </c>
+      <c r="B202">
+        <v>0.0536145311166809</v>
+      </c>
+      <c r="C202">
+        <v>2930</v>
+      </c>
+      <c r="D202">
+        <v>7.7481595567505</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203">
+        <v>8.5</v>
+      </c>
+      <c r="B203">
+        <v>0.0532976696590758</v>
+      </c>
+      <c r="C203">
+        <v>3402</v>
+      </c>
+      <c r="D203">
+        <v>8.24275983872338</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204">
+        <v>9</v>
+      </c>
+      <c r="B204">
+        <v>0.0530161145871474</v>
+      </c>
+      <c r="C204">
+        <v>3926</v>
+      </c>
+      <c r="D204">
+        <v>8.74722614715433</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205">
+        <v>9.5</v>
+      </c>
+      <c r="B205">
+        <v>0.0527356787572933</v>
+      </c>
+      <c r="C205">
+        <v>4266</v>
+      </c>
+      <c r="D205">
+        <v>9.24875254641385</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206">
+        <v>10</v>
+      </c>
+      <c r="B206">
+        <v>0.0524577602523578</v>
+      </c>
+      <c r="C206">
+        <v>4730</v>
+      </c>
+      <c r="D206">
+        <v>9.74564847205822</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207">
+        <v>10.5</v>
+      </c>
+      <c r="B207">
+        <v>0.0522426376758167</v>
+      </c>
+      <c r="C207">
+        <v>5510</v>
+      </c>
+      <c r="D207">
+        <v>10.2542063522575</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208">
+        <v>11</v>
+      </c>
+      <c r="B208">
+        <v>0.0520093342418595</v>
+      </c>
+      <c r="C208">
+        <v>5562</v>
+      </c>
+      <c r="D208">
+        <v>10.7542478228895</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209">
+        <v>11.5</v>
+      </c>
+      <c r="B209">
+        <v>0.0518161065492913</v>
+      </c>
+      <c r="C209">
+        <v>6410</v>
+      </c>
+      <c r="D209">
+        <v>11.244987895373</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210">
+        <v>12</v>
+      </c>
+      <c r="B210">
+        <v>0.0516198913290911</v>
+      </c>
+      <c r="C210">
+        <v>6894</v>
+      </c>
+      <c r="D210">
+        <v>11.7450714339387</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211">
+        <v>12.5</v>
+      </c>
+      <c r="B211">
+        <v>0.051409082960223</v>
+      </c>
+      <c r="C211">
+        <v>7490</v>
+      </c>
+      <c r="D211">
+        <v>12.2441426243554</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212">
+        <v>13</v>
+      </c>
+      <c r="B212">
+        <v>0.0511913387329072</v>
+      </c>
+      <c r="C212">
+        <v>8258</v>
+      </c>
+      <c r="D212">
+        <v>12.7444225452559</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213">
+        <v>13.5</v>
+      </c>
+      <c r="B213">
+        <v>0.0509977003508524</v>
+      </c>
+      <c r="C213">
+        <v>8994</v>
+      </c>
+      <c r="D213">
+        <v>13.2528519154988</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214">
+        <v>14</v>
+      </c>
+      <c r="B214">
+        <v>0.0508453600138596</v>
+      </c>
+      <c r="C214">
+        <v>9446</v>
+      </c>
+      <c r="D214">
+        <v>13.7542803671108</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215">
+        <v>14.5</v>
+      </c>
+      <c r="B215">
+        <v>0.0507101516586001</v>
+      </c>
+      <c r="C215">
+        <v>9978</v>
+      </c>
+      <c r="D215">
+        <v>14.2483018118451</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216">
+        <v>15</v>
+      </c>
+      <c r="B216">
+        <v>0.0505824226904095</v>
+      </c>
+      <c r="C216">
+        <v>11138</v>
+      </c>
+      <c r="D216">
+        <v>14.7478143756516</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217">
+        <v>15.5</v>
+      </c>
+      <c r="B217">
+        <v>0.0504515606249589</v>
+      </c>
+      <c r="C217">
+        <v>11406</v>
+      </c>
+      <c r="D217">
+        <v>15.2452282287867</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218">
+        <v>16</v>
+      </c>
+      <c r="B218">
+        <v>0.0502989873260437</v>
+      </c>
+      <c r="C218">
+        <v>12575</v>
+      </c>
+      <c r="D218">
+        <v>15.7433814113418</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <v>16.5</v>
+      </c>
+      <c r="B219">
+        <v>0.0501661740085702</v>
+      </c>
+      <c r="C219">
+        <v>12848</v>
+      </c>
+      <c r="D219">
+        <v>16.2480191911098</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <v>17</v>
+      </c>
+      <c r="B220">
+        <v>0.0500300500721085</v>
+      </c>
+      <c r="C220">
+        <v>12060</v>
+      </c>
+      <c r="D220">
+        <v>16.7498118527173</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <v>17.5</v>
+      </c>
+      <c r="B221">
+        <v>0.0499062791835329</v>
+      </c>
+      <c r="C221">
+        <v>11804</v>
+      </c>
+      <c r="D221">
+        <v>17.2477889982035</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <v>18</v>
+      </c>
+      <c r="B222">
+        <v>0.0497558728109345</v>
+      </c>
+      <c r="C222">
+        <v>11016</v>
+      </c>
+      <c r="D222">
+        <v>17.7466461218484</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>18.5</v>
+      </c>
+      <c r="B223">
+        <v>0.049619167720046</v>
+      </c>
+      <c r="C223">
+        <v>10700</v>
+      </c>
+      <c r="D223">
+        <v>18.2476461964778</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>19</v>
+      </c>
+      <c r="B224">
+        <v>0.0495260026719835</v>
+      </c>
+      <c r="C224">
+        <v>9756</v>
+      </c>
+      <c r="D224">
+        <v>18.7461608461768</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <v>19.5</v>
+      </c>
+      <c r="B225">
+        <v>0.0494382424863235</v>
+      </c>
+      <c r="C225">
+        <v>9224</v>
+      </c>
+      <c r="D225">
+        <v>19.2443623593903</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226">
+        <v>20</v>
+      </c>
+      <c r="B226">
+        <v>0.0493564342567741</v>
+      </c>
+      <c r="C226">
+        <v>8408</v>
+      </c>
+      <c r="D226">
+        <v>19.7427539394596</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227">
+        <v>20.5</v>
+      </c>
+      <c r="B227">
+        <v>0.0492738487255938</v>
+      </c>
+      <c r="C227">
+        <v>7452</v>
+      </c>
+      <c r="D227">
+        <v>20.2349524648069</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228">
+        <v>21</v>
+      </c>
+      <c r="B228">
+        <v>0.0492199019952254</v>
+      </c>
+      <c r="C228">
+        <v>7040</v>
+      </c>
+      <c r="D228">
+        <v>20.7366941177926</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229">
+        <v>21.5</v>
+      </c>
+      <c r="B229">
+        <v>0.0491662225362771</v>
+      </c>
+      <c r="C229">
+        <v>5820</v>
+      </c>
+      <c r="D229">
+        <v>21.2419860619221</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230">
+        <v>22</v>
+      </c>
+      <c r="B230">
+        <v>0.0491668138347688</v>
+      </c>
+      <c r="C230">
+        <v>4880</v>
+      </c>
+      <c r="D230">
+        <v>21.7372039907627</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231">
+        <v>22.5</v>
+      </c>
+      <c r="B231">
+        <v>0.049152023423978</v>
+      </c>
+      <c r="C231">
+        <v>3936</v>
+      </c>
+      <c r="D231">
+        <v>22.2302479362391</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232">
+        <v>23</v>
+      </c>
+      <c r="B232">
+        <v>0.0491141675114035</v>
+      </c>
+      <c r="C232">
+        <v>2999</v>
+      </c>
+      <c r="D232">
+        <v>22.7334385317465</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233">
+        <v>23.5</v>
+      </c>
+      <c r="B233">
+        <v>0.0490822923292807</v>
+      </c>
+      <c r="C233">
+        <v>2180</v>
+      </c>
+      <c r="D233">
+        <v>23.2369587045059</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234">
+        <v>24</v>
+      </c>
+      <c r="B234">
+        <v>0.0490197358308015</v>
+      </c>
+      <c r="C234">
+        <v>1620</v>
+      </c>
+      <c r="D234">
+        <v>23.7279225769148</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235">
+        <v>24.5</v>
+      </c>
+      <c r="B235">
+        <v>0.0488874107007159</v>
+      </c>
+      <c r="C235">
+        <v>1208</v>
+      </c>
+      <c r="D235">
+        <v>24.2151258882127</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236">
+        <v>25</v>
+      </c>
+      <c r="B236">
+        <v>0.0488937847680094</v>
+      </c>
+      <c r="C236">
+        <v>942</v>
+      </c>
+      <c r="D236">
+        <v>24.7383759194601</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <v>25.5</v>
+      </c>
+      <c r="B237">
+        <v>0.0489536703449406</v>
+      </c>
+      <c r="C237">
+        <v>584</v>
+      </c>
+      <c r="D237">
+        <v>25.2823739766508</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <v>26</v>
+      </c>
+      <c r="B238">
+        <v>0.049027939917336</v>
+      </c>
+      <c r="C238">
+        <v>284</v>
+      </c>
+      <c r="D238">
+        <v>25.7666230311241</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <v>26.5</v>
+      </c>
+      <c r="B239">
+        <v>0.0490736564000448</v>
+      </c>
+      <c r="C239">
+        <v>192</v>
+      </c>
+      <c r="D239">
+        <v>26.1687296580041</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <v>27</v>
+      </c>
+      <c r="B240">
+        <v>0.0491525943462665</v>
+      </c>
+      <c r="C240">
+        <v>104</v>
+      </c>
+      <c r="D240">
+        <v>26.6774814912972</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>27.5</v>
+      </c>
+      <c r="B241">
+        <v>0.0496870676676432</v>
+      </c>
+      <c r="C241">
+        <v>24</v>
+      </c>
+      <c r="D241">
+        <v>27.2129968013123</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>28</v>
+      </c>
+      <c r="B242">
+        <v>0.0503158569335938</v>
+      </c>
+      <c r="C242">
+        <v>1</v>
+      </c>
+      <c r="D242">
+        <v>27.712812921102</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x displacement (um)</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>0</v>
+      </c>
+      <c r="B244">
+        <v>0.225189208984375</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>0.5</v>
+      </c>
+      <c r="B245">
+        <v>0.135887145996094</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>1</v>
+      </c>
+      <c r="B246">
+        <v>0.0884857177734375</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>1.5</v>
+      </c>
+      <c r="B247">
+        <v>0.0660133361816406</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>2</v>
+      </c>
+      <c r="B248">
+        <v>0.0583648681640625</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>2.5</v>
+      </c>
+      <c r="B249">
+        <v>0.0555534362792969</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>3</v>
+      </c>
+      <c r="B250">
+        <v>0.0561485290527344</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>3.5</v>
+      </c>
+      <c r="B251">
+        <v>0.0557136535644531</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>4</v>
+      </c>
+      <c r="B252">
+        <v>0.0558509826660156</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <v>4.5</v>
+      </c>
+      <c r="B253">
+        <v>0.0555381774902344</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <v>5</v>
+      </c>
+      <c r="B254">
+        <v>0.0556907653808594</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>5.5</v>
+      </c>
+      <c r="B255">
+        <v>0.0558357238769531</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>6</v>
+      </c>
+      <c r="B256">
+        <v>0.0562477111816406</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <v>6.5</v>
+      </c>
+      <c r="B257">
+        <v>0.055816650390625</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <v>7</v>
+      </c>
+      <c r="B258">
+        <v>0.05517578125</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <v>7.5</v>
+      </c>
+      <c r="B259">
+        <v>0.0544929504394531</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <v>8</v>
+      </c>
+      <c r="B260">
+        <v>0.0539741516113281</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <v>8.5</v>
+      </c>
+      <c r="B261">
+        <v>0.0537872314453125</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <v>9</v>
+      </c>
+      <c r="B262">
+        <v>0.0542984008789062</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263">
+        <v>9.5</v>
+      </c>
+      <c r="B263">
+        <v>0.0544509887695312</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <v>10</v>
+      </c>
+      <c r="B264">
+        <v>0.0543746948242188</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <v>10.5</v>
+      </c>
+      <c r="B265">
+        <v>0.0538902282714844</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>11</v>
+      </c>
+      <c r="B266">
+        <v>0.0543060302734375</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>11.5</v>
+      </c>
+      <c r="B267">
+        <v>0.0541839599609375</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>12</v>
+      </c>
+      <c r="B268">
+        <v>0.0541152954101562</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>12.5</v>
+      </c>
+      <c r="B269">
+        <v>0.0542488098144531</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <v>13</v>
+      </c>
+      <c r="B270">
+        <v>0.0540924072265625</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <v>13.5</v>
+      </c>
+      <c r="B271">
+        <v>0.0541496276855469</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272">
+        <v>14</v>
+      </c>
+      <c r="B272">
+        <v>0.0543899536132812</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273">
+        <v>14.5</v>
+      </c>
+      <c r="B273">
+        <v>0.0542984008789062</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>15</v>
+      </c>
+      <c r="B274">
+        <v>0.0547676086425781</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>15.5</v>
+      </c>
+      <c r="B275">
+        <v>0.0555267333984375</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>16</v>
+      </c>
+      <c r="B276">
+        <v>0.0560073852539062</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y displacement (um)</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>0</v>
+      </c>
+      <c r="B278">
+        <v>0.225189208984375</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>0.5</v>
+      </c>
+      <c r="B279">
+        <v>0.124134063720703</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280">
+        <v>1</v>
+      </c>
+      <c r="B280">
+        <v>0.0783233642578125</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281">
+        <v>1.5</v>
+      </c>
+      <c r="B281">
+        <v>0.0606651306152344</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282">
+        <v>2</v>
+      </c>
+      <c r="B282">
+        <v>0.0583305358886719</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283">
+        <v>2.5</v>
+      </c>
+      <c r="B283">
+        <v>0.0580062866210938</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284">
+        <v>3</v>
+      </c>
+      <c r="B284">
+        <v>0.058746337890625</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <v>3.5</v>
+      </c>
+      <c r="B285">
+        <v>0.0576515197753906</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286">
+        <v>4</v>
+      </c>
+      <c r="B286">
+        <v>0.0567970275878906</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287">
+        <v>4.5</v>
+      </c>
+      <c r="B287">
+        <v>0.056427001953125</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288">
+        <v>5</v>
+      </c>
+      <c r="B288">
+        <v>0.0561943054199219</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289">
+        <v>5.5</v>
+      </c>
+      <c r="B289">
+        <v>0.0555877685546875</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290">
+        <v>6</v>
+      </c>
+      <c r="B290">
+        <v>0.0549850463867188</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291">
+        <v>6.5</v>
+      </c>
+      <c r="B291">
+        <v>0.0536041259765625</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292">
+        <v>7</v>
+      </c>
+      <c r="B292">
+        <v>0.0531044006347656</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293">
+        <v>7.5</v>
+      </c>
+      <c r="B293">
+        <v>0.0531044006347656</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294">
+        <v>8</v>
+      </c>
+      <c r="B294">
+        <v>0.0523490905761719</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295">
+        <v>8.5</v>
+      </c>
+      <c r="B295">
+        <v>0.0514907836914062</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296">
+        <v>9</v>
+      </c>
+      <c r="B296">
+        <v>0.0506629943847656</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297">
+        <v>9.5</v>
+      </c>
+      <c r="B297">
+        <v>0.049957275390625</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298">
+        <v>10</v>
+      </c>
+      <c r="B298">
+        <v>0.0500526428222656</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299">
+        <v>10.5</v>
+      </c>
+      <c r="B299">
+        <v>0.0498504638671875</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300">
+        <v>11</v>
+      </c>
+      <c r="B300">
+        <v>0.0494155883789062</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301">
+        <v>11.5</v>
+      </c>
+      <c r="B301">
+        <v>0.0486984252929688</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302">
+        <v>12</v>
+      </c>
+      <c r="B302">
+        <v>0.0487709045410156</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303">
+        <v>12.5</v>
+      </c>
+      <c r="B303">
+        <v>0.0489883422851562</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304">
+        <v>13</v>
+      </c>
+      <c r="B304">
+        <v>0.0493545532226562</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305">
+        <v>13.5</v>
+      </c>
+      <c r="B305">
+        <v>0.0488090515136719</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306">
+        <v>14</v>
+      </c>
+      <c r="B306">
+        <v>0.0488090515136719</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307">
+        <v>14.5</v>
+      </c>
+      <c r="B307">
+        <v>0.049072265625</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308">
+        <v>15</v>
+      </c>
+      <c r="B308">
+        <v>0.0489463806152344</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309">
+        <v>15.5</v>
+      </c>
+      <c r="B309">
+        <v>0.0488128662109375</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310">
+        <v>16</v>
+      </c>
+      <c r="B310">
+        <v>0.0489425659179687</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z displacement (um)</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312">
+        <v>0</v>
+      </c>
+      <c r="B312">
+        <v>0.225189208984375</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313">
+        <v>0.5</v>
+      </c>
+      <c r="B313">
+        <v>0.120635986328125</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314">
+        <v>1</v>
+      </c>
+      <c r="B314">
+        <v>0.0778236389160156</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315">
+        <v>1.5</v>
+      </c>
+      <c r="B315">
+        <v>0.0600738525390625</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316">
+        <v>2</v>
+      </c>
+      <c r="B316">
+        <v>0.0586624145507812</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317">
+        <v>2.5</v>
+      </c>
+      <c r="B317">
+        <v>0.0576972961425781</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318">
+        <v>3</v>
+      </c>
+      <c r="B318">
+        <v>0.0579261779785156</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319">
+        <v>3.5</v>
+      </c>
+      <c r="B319">
+        <v>0.0578460693359375</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320">
+        <v>4</v>
+      </c>
+      <c r="B320">
+        <v>0.0569267272949219</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321">
+        <v>4.5</v>
+      </c>
+      <c r="B321">
+        <v>0.056793212890625</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322">
+        <v>5</v>
+      </c>
+      <c r="B322">
+        <v>0.0568466186523438</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323">
+        <v>5.5</v>
+      </c>
+      <c r="B323">
+        <v>0.0558509826660156</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324">
+        <v>6</v>
+      </c>
+      <c r="B324">
+        <v>0.0550804138183594</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325">
+        <v>6.5</v>
+      </c>
+      <c r="B325">
+        <v>0.0540885925292969</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326">
+        <v>7</v>
+      </c>
+      <c r="B326">
+        <v>0.0530738830566406</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327">
+        <v>7.5</v>
+      </c>
+      <c r="B327">
+        <v>0.0528297424316406</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328">
+        <v>8</v>
+      </c>
+      <c r="B328">
+        <v>0.0530052185058594</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329">
+        <v>8.5</v>
+      </c>
+      <c r="B329">
+        <v>0.0531997680664062</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330">
+        <v>9</v>
+      </c>
+      <c r="B330">
+        <v>0.0532112121582031</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331">
+        <v>9.5</v>
+      </c>
+      <c r="B331">
+        <v>0.0528297424316406</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332">
+        <v>10</v>
+      </c>
+      <c r="B332">
+        <v>0.0524864196777344</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333">
+        <v>10.5</v>
+      </c>
+      <c r="B333">
+        <v>0.0523262023925781</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334">
+        <v>11</v>
+      </c>
+      <c r="B334">
+        <v>0.0520362854003906</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335">
+        <v>11.5</v>
+      </c>
+      <c r="B335">
+        <v>0.0520286560058594</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336">
+        <v>12</v>
+      </c>
+      <c r="B336">
+        <v>0.0513763427734375</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337">
+        <v>12.5</v>
+      </c>
+      <c r="B337">
+        <v>0.0514068603515625</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338">
+        <v>13</v>
+      </c>
+      <c r="B338">
+        <v>0.051849365234375</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339">
+        <v>13.5</v>
+      </c>
+      <c r="B339">
+        <v>0.0516815185546875</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340">
+        <v>14</v>
+      </c>
+      <c r="B340">
+        <v>0.0515213012695312</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341">
+        <v>14.5</v>
+      </c>
+      <c r="B341">
+        <v>0.0513420104980469</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342">
+        <v>15</v>
+      </c>
+      <c r="B342">
+        <v>0.0516281127929688</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343">
+        <v>15.5</v>
+      </c>
+      <c r="B343">
+        <v>0.0514640808105469</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344">
+        <v>16</v>
+      </c>
+      <c r="B344">
+        <v>0.0511093139648437</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>